--- a/dictionary.xlsx
+++ b/dictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob.sharepoint.com/teams/grp-Bristol_TAG-MTA-MS/Shared Documents/MTA-MS/Working Folder_HE/MS Models/Git Repo/MS-MTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="269" documentId="8_{76071419-A7CB-4F17-9D34-0E781EDA7FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A15F5A5-248C-410D-BDD1-67B33C2392D5}"/>
+  <xr:revisionPtr revIDLastSave="281" documentId="8_{76071419-A7CB-4F17-9D34-0E781EDA7FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43B0633A-DB31-4F70-934F-F45AD895365A}"/>
   <bookViews>
-    <workbookView xWindow="9420" yWindow="285" windowWidth="14790" windowHeight="12510" firstSheet="4" activeTab="4" xr2:uid="{C900376C-AEC5-4C6A-B806-8D6753BB10C1}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="13800" activeTab="1" xr2:uid="{C900376C-AEC5-4C6A-B806-8D6753BB10C1}"/>
   </bookViews>
   <sheets>
     <sheet name="flags" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
   <si>
     <t>edss</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>f.dead</t>
+  </si>
+  <si>
+    <t>ae_</t>
+  </si>
+  <si>
+    <t>rlps_</t>
   </si>
 </sst>
 </file>
@@ -988,8 +994,9 @@
         <f t="shared" si="1"/>
         <v>f.tx.ib1a</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>35</v>
+      <c r="D33" s="4" t="str">
+        <f>costs!F9</f>
+        <v>ib1a</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -997,8 +1004,9 @@
         <f t="shared" si="1"/>
         <v>f.tx.ib1b</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>36</v>
+      <c r="D34" s="4" t="str">
+        <f>costs!F10</f>
+        <v>ib1b</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1006,8 +1014,9 @@
         <f t="shared" si="1"/>
         <v>f.tx.glat</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>37</v>
+      <c r="D35" s="4" t="str">
+        <f>costs!F11</f>
+        <v>glat</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1015,8 +1024,9 @@
         <f t="shared" si="1"/>
         <v>f.tx.ofat</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>38</v>
+      <c r="D36" s="4" t="str">
+        <f>costs!F12</f>
+        <v>ofat</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1024,8 +1034,9 @@
         <f t="shared" si="1"/>
         <v>f.tx.pone</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>39</v>
+      <c r="D37" s="4" t="str">
+        <f>costs!F13</f>
+        <v>pone</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1033,8 +1044,9 @@
         <f t="shared" si="1"/>
         <v>f.tx.ahsct</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>40</v>
+      <c r="D38" s="4" t="str">
+        <f>costs!F14</f>
+        <v>ahsct</v>
       </c>
     </row>
   </sheetData>
@@ -1186,7 +1198,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13B9B9E5-CA49-41F7-9A52-F58BFE2734C8}">
-  <dimension ref="A2:F33"/>
+  <dimension ref="A2:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
@@ -1275,7 +1287,9 @@
         <v>c.m_edss3</v>
       </c>
       <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3">
         <v>3</v>
@@ -1290,7 +1304,9 @@
         <v>c.m_edss4</v>
       </c>
       <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3">
         <v>4</v>
@@ -1310,6 +1326,9 @@
       <c r="E9" s="3">
         <v>5</v>
       </c>
+      <c r="F9" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
@@ -1322,6 +1341,9 @@
       <c r="E10" s="3">
         <v>6</v>
       </c>
+      <c r="F10" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
@@ -1334,6 +1356,9 @@
       <c r="E11" s="3">
         <v>7</v>
       </c>
+      <c r="F11" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
@@ -1346,6 +1371,9 @@
       <c r="E12" s="3">
         <v>8</v>
       </c>
+      <c r="F12" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
@@ -1358,6 +1386,9 @@
       <c r="E13" s="3">
         <v>9</v>
       </c>
+      <c r="F13" s="4" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
@@ -1367,6 +1398,9 @@
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
+      <c r="F14" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
@@ -1461,6 +1495,42 @@
       <c r="A33" t="str">
         <f>_xlfn.CONCAT($B$4,$C$6,F8)</f>
         <v>c.tx_alem</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="str">
+        <f t="shared" ref="A34:A39" si="2">_xlfn.CONCAT($B$4,$C$6,F9)</f>
+        <v>c.tx_ib1a</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="str">
+        <f t="shared" si="2"/>
+        <v>c.tx_ib1b</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="str">
+        <f t="shared" si="2"/>
+        <v>c.tx_glat</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="str">
+        <f t="shared" si="2"/>
+        <v>c.tx_ofat</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="str">
+        <f t="shared" si="2"/>
+        <v>c.tx_pone</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="str">
+        <f t="shared" si="2"/>
+        <v>c.tx_ahsct</v>
       </c>
     </row>
   </sheetData>
@@ -2744,15 +2814,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACE3D2A8E3060445845CB33F649944D9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7c8efc5d897a5a54c153d61be50fc1e0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a4e98822-f433-4c96-8830-5cb2d7491f7d" xmlns:ns3="adc125f1-7df9-46f4-a9a7-022dd426a2bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7c927ce20f93a00fedc297caf603d12c" ns2:_="" ns3:_="">
     <xsd:import namespace="a4e98822-f433-4c96-8830-5cb2d7491f7d"/>
@@ -2963,6 +3024,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1177130-4AE0-4BC3-812F-C368639BAA24}">
   <ds:schemaRefs>
@@ -2974,14 +3044,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D1F9637-7F0E-4FBA-AACC-902D66183076}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CEAF85B-B364-425F-B961-632DD00472C0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2998,4 +3060,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D1F9637-7F0E-4FBA-AACC-902D66183076}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>